--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -5,7 +5,7 @@
   <workbookPr backupFile="false" showObjects="all" date1904="false"/>
   <workbookProtection/>
   <bookViews>
-    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="1"/>
+    <workbookView showHorizontalScroll="true" showVerticalScroll="true" showSheetTabs="true" xWindow="0" yWindow="0" windowWidth="16384" windowHeight="8192" tabRatio="500" firstSheet="0" activeTab="0"/>
   </bookViews>
   <sheets>
     <sheet name="spawns" sheetId="1" state="visible" r:id="rId3"/>
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="11">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
   <si>
     <t xml:space="preserve">levelId</t>
   </si>
@@ -45,6 +45,9 @@
   </si>
   <si>
     <t xml:space="preserve">data</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10010_1,10000_3</t>
   </si>
   <si>
     <t xml:space="preserve">10010_3,10000_1</t>
@@ -99,6 +102,7 @@
       <color theme="1"/>
       <name val="Liberation Mono;Courier New;DejaVu Sans Mono"/>
       <family val="3"/>
+      <charset val="1"/>
     </font>
   </fonts>
   <fills count="4">
@@ -162,8 +166,12 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="12">
+  <cellXfs count="8">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
+      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
+      <protection locked="true" hidden="false"/>
+    </xf>
+    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -171,27 +179,11 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="4" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
     <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="0" fillId="3" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -203,11 +195,7 @@
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
-    <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="false" applyProtection="false">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false">
+    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -463,21 +451,21 @@
   <dimension ref="A1:H1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="0" width="7.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="0" width="17.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.93"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="1" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>1</v>
-      </c>
-      <c r="C1" s="1" t="s">
+      <c r="A1" s="2" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="2" t="s">
+        <v>1</v>
+      </c>
+      <c r="C1" s="2" t="s">
         <v>2</v>
       </c>
-      <c r="D1" s="1" t="s">
+      <c r="D1" s="2" t="s">
         <v>3</v>
       </c>
       <c r="E1" s="2" t="s">
@@ -494,315 +482,315 @@
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C2" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E2" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F2" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G2" s="0" t="n">
-        <v>50</v>
-      </c>
-      <c r="H2" s="0" t="s">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C2" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E2" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F2" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G2" s="1" t="n">
+        <v>400</v>
+      </c>
+      <c r="H2" s="1" t="s">
         <v>8</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B3" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="4" t="n">
+      <c r="A3" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B3" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C3" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E3" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F3" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G3" s="0" t="n">
+      <c r="D3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E3" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F3" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G3" s="1" t="n">
         <v>51</v>
       </c>
-      <c r="H3" s="0" t="s">
-        <v>8</v>
+      <c r="H3" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B4" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="5" t="n">
+      <c r="A4" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B4" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C4" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E4" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F4" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G4" s="0" t="n">
+      <c r="D4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E4" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F4" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G4" s="1" t="n">
         <v>52</v>
       </c>
-      <c r="H4" s="0" t="s">
-        <v>8</v>
+      <c r="H4" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B5" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="5" t="n">
+      <c r="A5" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B5" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="C5" s="3" t="n">
         <v>4</v>
       </c>
-      <c r="D5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E5" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F5" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G5" s="0" t="n">
+      <c r="D5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E5" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F5" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G5" s="1" t="n">
         <v>53</v>
       </c>
-      <c r="H5" s="0" t="s">
-        <v>8</v>
+      <c r="H5" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A6" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B6" s="6" t="n">
+      <c r="A6" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B6" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C6" s="6" t="n">
-        <v>1</v>
-      </c>
-      <c r="D6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E6" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F6" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G6" s="0" t="n">
+      <c r="C6" s="4" t="n">
+        <v>1</v>
+      </c>
+      <c r="D6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E6" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F6" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G6" s="1" t="n">
         <v>54</v>
       </c>
-      <c r="H6" s="0" t="s">
-        <v>8</v>
+      <c r="H6" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A7" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B7" s="6" t="n">
+      <c r="A7" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C7" s="6" t="n">
+      <c r="C7" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="D7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E7" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F7" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G7" s="0" t="n">
+      <c r="D7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E7" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F7" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G7" s="1" t="n">
         <v>55</v>
       </c>
-      <c r="H7" s="0" t="s">
-        <v>8</v>
+      <c r="H7" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A8" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B8" s="6" t="n">
+      <c r="A8" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B8" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="7" t="n">
+      <c r="C8" s="4" t="n">
         <v>3</v>
       </c>
-      <c r="D8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E8" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F8" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G8" s="0" t="n">
+      <c r="D8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E8" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F8" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G8" s="1" t="n">
         <v>56</v>
       </c>
-      <c r="H8" s="0" t="s">
-        <v>8</v>
+      <c r="H8" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A9" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B9" s="6" t="n">
+      <c r="A9" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B9" s="4" t="n">
         <v>2</v>
       </c>
-      <c r="C9" s="7" t="n">
+      <c r="C9" s="4" t="n">
         <v>4</v>
       </c>
-      <c r="D9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E9" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F9" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G9" s="0" t="n">
+      <c r="D9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E9" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F9" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G9" s="1" t="n">
         <v>57</v>
       </c>
-      <c r="H9" s="0" t="s">
-        <v>8</v>
+      <c r="H9" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="4" t="n">
+      <c r="A10" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="4" t="n">
-        <v>1</v>
-      </c>
-      <c r="D10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E10" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F10" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G10" s="0" t="n">
+      <c r="C10" s="3" t="n">
+        <v>1</v>
+      </c>
+      <c r="D10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E10" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F10" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G10" s="1" t="n">
         <v>58</v>
       </c>
-      <c r="H10" s="0" t="s">
-        <v>8</v>
+      <c r="H10" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="4" t="n">
+      <c r="A11" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B11" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C11" s="4" t="n">
+      <c r="C11" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="D11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="0" t="n">
+      <c r="D11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E11" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F11" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G11" s="1" t="n">
         <v>59</v>
       </c>
-      <c r="H11" s="0" t="s">
-        <v>8</v>
+      <c r="H11" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="4" t="n">
+      <c r="A12" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="C12" s="5" t="n">
+      <c r="C12" s="3" t="n">
         <v>3</v>
       </c>
-      <c r="D12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="0" t="n">
+      <c r="D12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E12" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F12" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G12" s="1" t="n">
         <v>60</v>
       </c>
-      <c r="H12" s="0" t="s">
-        <v>8</v>
+      <c r="H12" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="8" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="9" t="n">
+      <c r="A13" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B13" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C13" s="10" t="n">
+      <c r="C13" s="6" t="n">
         <v>4</v>
       </c>
-      <c r="D13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="3" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="0" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="0" t="n">
+      <c r="D13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="E13" s="1" t="n">
+        <v>0</v>
+      </c>
+      <c r="F13" s="1" t="n">
+        <v>10</v>
+      </c>
+      <c r="G13" s="1" t="n">
         <v>61</v>
       </c>
-      <c r="H13" s="0" t="s">
-        <v>8</v>
+      <c r="H13" s="1" t="s">
+        <v>9</v>
       </c>
     </row>
     <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
@@ -826,20 +814,20 @@
   <dimension ref="A1:B2"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <sheetData>
-    <row r="1" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="11" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="0" t="s">
-        <v>9</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="0" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="0" t="s">
-        <v>10</v>
+    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A1" s="7" t="s">
+        <v>0</v>
+      </c>
+      <c r="B1" s="1" t="s">
+        <v>10</v>
+      </c>
+    </row>
+    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
+      <c r="A2" s="1" t="n">
+        <v>1</v>
+      </c>
+      <c r="B2" s="1" t="s">
+        <v>11</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="23" uniqueCount="12">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="14">
   <si>
     <t xml:space="preserve">levelId</t>
   </si>
@@ -44,10 +44,16 @@
     <t xml:space="preserve">power</t>
   </si>
   <si>
+    <t xml:space="preserve">spawnId</t>
+  </si>
+  <si>
     <t xml:space="preserve">data</t>
   </si>
   <si>
-    <t xml:space="preserve">10010_1,10000_3</t>
+    <t xml:space="preserve">Spawn_Random</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10000_3</t>
   </si>
   <si>
     <t xml:space="preserve">10010_3,10000_1</t>
@@ -448,11 +454,12 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:H1048576"/>
+  <dimension ref="A1:I13"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="17.43"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.43"/>
   </cols>
   <sheetData>
     <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -480,6 +487,9 @@
       <c r="H1" s="2" t="s">
         <v>7</v>
       </c>
+      <c r="I1" s="2" t="s">
+        <v>8</v>
+      </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A2" s="1" t="n">
@@ -501,10 +511,13 @@
         <v>10</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>400</v>
+        <v>51</v>
       </c>
       <c r="H2" s="1" t="s">
-        <v>8</v>
+        <v>9</v>
+      </c>
+      <c r="I2" s="1" t="s">
+        <v>10</v>
       </c>
     </row>
     <row r="3" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -532,6 +545,9 @@
       <c r="H3" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I3" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="4" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A4" s="1" t="n">
@@ -558,6 +574,9 @@
       <c r="H4" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I4" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="5" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A5" s="1" t="n">
@@ -584,6 +603,9 @@
       <c r="H5" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I5" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="6" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A6" s="1" t="n">
@@ -610,6 +632,9 @@
       <c r="H6" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I6" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="7" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A7" s="1" t="n">
@@ -636,6 +661,9 @@
       <c r="H7" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I7" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="8" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A8" s="1" t="n">
@@ -662,6 +690,9 @@
       <c r="H8" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I8" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="9" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A9" s="1" t="n">
@@ -688,6 +719,9 @@
       <c r="H9" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I9" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A10" s="1" t="n">
@@ -714,6 +748,9 @@
       <c r="H10" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I10" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A11" s="1" t="n">
@@ -740,6 +777,9 @@
       <c r="H11" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I11" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A12" s="1" t="n">
@@ -766,6 +806,9 @@
       <c r="H12" s="1" t="s">
         <v>9</v>
       </c>
+      <c r="I12" s="1" t="s">
+        <v>11</v>
+      </c>
     </row>
     <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
       <c r="A13" s="5" t="n">
@@ -792,9 +835,10 @@
       <c r="H13" s="1" t="s">
         <v>9</v>
       </c>
-    </row>
-    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
-    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+      <c r="I13" s="1" t="s">
+        <v>11</v>
+      </c>
+    </row>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
@@ -819,7 +863,7 @@
         <v>0</v>
       </c>
       <c r="B1" s="1" t="s">
-        <v>10</v>
+        <v>12</v>
       </c>
     </row>
     <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
@@ -827,7 +871,7 @@
         <v>1</v>
       </c>
       <c r="B2" s="1" t="s">
-        <v>11</v>
+        <v>13</v>
       </c>
     </row>
   </sheetData>

--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -21,7 +21,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="36" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
   <si>
     <t xml:space="preserve">levelId</t>
   </si>
@@ -454,7 +454,7 @@
   <sheetPr filterMode="false">
     <pageSetUpPr fitToPage="false"/>
   </sheetPr>
-  <dimension ref="A1:I13"/>
+  <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.93"/>
@@ -524,12 +524,12 @@
       <c r="A3" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B3" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C3" s="3" t="n">
+      <c r="B3" s="4" t="n">
         <v>2</v>
       </c>
+      <c r="C3" s="4" t="n">
+        <v>1</v>
+      </c>
       <c r="D3" s="1" t="n">
         <v>0</v>
       </c>
@@ -540,7 +540,7 @@
         <v>10</v>
       </c>
       <c r="G3" s="1" t="n">
-        <v>51</v>
+        <v>54</v>
       </c>
       <c r="H3" s="1" t="s">
         <v>9</v>
@@ -553,11 +553,11 @@
       <c r="A4" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B4" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C4" s="3" t="n">
-        <v>3</v>
+      <c r="B4" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C4" s="4" t="n">
+        <v>2</v>
       </c>
       <c r="D4" s="1" t="n">
         <v>0</v>
@@ -569,7 +569,7 @@
         <v>10</v>
       </c>
       <c r="G4" s="1" t="n">
-        <v>52</v>
+        <v>55</v>
       </c>
       <c r="H4" s="1" t="s">
         <v>9</v>
@@ -582,11 +582,11 @@
       <c r="A5" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B5" s="3" t="n">
-        <v>1</v>
-      </c>
-      <c r="C5" s="3" t="n">
-        <v>4</v>
+      <c r="B5" s="4" t="n">
+        <v>2</v>
+      </c>
+      <c r="C5" s="4" t="n">
+        <v>3</v>
       </c>
       <c r="D5" s="1" t="n">
         <v>0</v>
@@ -598,7 +598,7 @@
         <v>10</v>
       </c>
       <c r="G5" s="1" t="n">
-        <v>53</v>
+        <v>56</v>
       </c>
       <c r="H5" s="1" t="s">
         <v>9</v>
@@ -615,7 +615,7 @@
         <v>2</v>
       </c>
       <c r="C6" s="4" t="n">
-        <v>1</v>
+        <v>4</v>
       </c>
       <c r="D6" s="1" t="n">
         <v>0</v>
@@ -627,7 +627,7 @@
         <v>10</v>
       </c>
       <c r="G6" s="1" t="n">
-        <v>54</v>
+        <v>57</v>
       </c>
       <c r="H6" s="1" t="s">
         <v>9</v>
@@ -640,11 +640,11 @@
       <c r="A7" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B7" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C7" s="4" t="n">
-        <v>2</v>
+      <c r="B7" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C7" s="3" t="n">
+        <v>1</v>
       </c>
       <c r="D7" s="1" t="n">
         <v>0</v>
@@ -656,7 +656,7 @@
         <v>10</v>
       </c>
       <c r="G7" s="1" t="n">
-        <v>55</v>
+        <v>58</v>
       </c>
       <c r="H7" s="1" t="s">
         <v>9</v>
@@ -669,12 +669,12 @@
       <c r="A8" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B8" s="4" t="n">
+      <c r="B8" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C8" s="3" t="n">
         <v>2</v>
       </c>
-      <c r="C8" s="4" t="n">
-        <v>3</v>
-      </c>
       <c r="D8" s="1" t="n">
         <v>0</v>
       </c>
@@ -685,7 +685,7 @@
         <v>10</v>
       </c>
       <c r="G8" s="1" t="n">
-        <v>56</v>
+        <v>59</v>
       </c>
       <c r="H8" s="1" t="s">
         <v>9</v>
@@ -698,11 +698,11 @@
       <c r="A9" s="1" t="n">
         <v>1</v>
       </c>
-      <c r="B9" s="4" t="n">
-        <v>2</v>
-      </c>
-      <c r="C9" s="4" t="n">
-        <v>4</v>
+      <c r="B9" s="3" t="n">
+        <v>3</v>
+      </c>
+      <c r="C9" s="3" t="n">
+        <v>3</v>
       </c>
       <c r="D9" s="1" t="n">
         <v>0</v>
@@ -714,7 +714,7 @@
         <v>10</v>
       </c>
       <c r="G9" s="1" t="n">
-        <v>57</v>
+        <v>60</v>
       </c>
       <c r="H9" s="1" t="s">
         <v>9</v>
@@ -724,14 +724,14 @@
       </c>
     </row>
     <row r="10" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A10" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B10" s="3" t="n">
+      <c r="A10" s="5" t="n">
+        <v>1</v>
+      </c>
+      <c r="B10" s="6" t="n">
         <v>3</v>
       </c>
-      <c r="C10" s="3" t="n">
-        <v>1</v>
+      <c r="C10" s="6" t="n">
+        <v>4</v>
       </c>
       <c r="D10" s="1" t="n">
         <v>0</v>
@@ -743,7 +743,7 @@
         <v>10</v>
       </c>
       <c r="G10" s="1" t="n">
-        <v>58</v>
+        <v>61</v>
       </c>
       <c r="H10" s="1" t="s">
         <v>9</v>
@@ -752,93 +752,9 @@
         <v>11</v>
       </c>
     </row>
-    <row r="11" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A11" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B11" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C11" s="3" t="n">
-        <v>2</v>
-      </c>
-      <c r="D11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E11" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F11" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G11" s="1" t="n">
-        <v>59</v>
-      </c>
-      <c r="H11" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I11" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="12" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A12" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="C12" s="3" t="n">
-        <v>3</v>
-      </c>
-      <c r="D12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E12" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F12" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G12" s="1" t="n">
-        <v>60</v>
-      </c>
-      <c r="H12" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I12" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
-    <row r="13" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A13" s="5" t="n">
-        <v>1</v>
-      </c>
-      <c r="B13" s="6" t="n">
-        <v>3</v>
-      </c>
-      <c r="C13" s="6" t="n">
-        <v>4</v>
-      </c>
-      <c r="D13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="E13" s="1" t="n">
-        <v>0</v>
-      </c>
-      <c r="F13" s="1" t="n">
-        <v>10</v>
-      </c>
-      <c r="G13" s="1" t="n">
-        <v>61</v>
-      </c>
-      <c r="H13" s="1" t="s">
-        <v>9</v>
-      </c>
-      <c r="I13" s="1" t="s">
-        <v>11</v>
-      </c>
-    </row>
+    <row r="1048574" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048575" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
+    <row r="1048576" customFormat="false" ht="12.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false"/>
   </sheetData>
   <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
   <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>

--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">Spawn_Random</t>
   </si>
   <si>
-    <t xml:space="preserve">10000_3</t>
+    <t xml:space="preserve">10000_1</t>
   </si>
   <si>
     <t xml:space="preserve">10010_3,10000_1</t>

--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -53,7 +53,7 @@
     <t xml:space="preserve">Spawn_Random</t>
   </si>
   <si>
-    <t xml:space="preserve">10000_1</t>
+    <t xml:space="preserve">10000_10, 10010_2</t>
   </si>
   <si>
     <t xml:space="preserve">10010_3,10000_1</t>
@@ -508,10 +508,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>10</v>
+        <v>100</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>51</v>
+        <v>1000</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>9</v>

--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -508,10 +508,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>100</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>1000</v>
+        <v>50</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>9</v>

--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -9,7 +9,6 @@
   </bookViews>
   <sheets>
     <sheet name="spawns" sheetId="1" state="visible" r:id="rId3"/>
-    <sheet name="datas" sheetId="2" state="visible" r:id="rId4"/>
   </sheets>
   <calcPr iterateCount="100" refMode="A1" iterate="false" iterateDelta="0.0001"/>
   <extLst>
@@ -21,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="30" uniqueCount="14">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="27" uniqueCount="12">
   <si>
     <t xml:space="preserve">levelId</t>
   </si>
@@ -57,12 +56,6 @@
   </si>
   <si>
     <t xml:space="preserve">10010_3,10000_1</t>
-  </si>
-  <si>
-    <t xml:space="preserve">levelDesign</t>
-  </si>
-  <si>
-    <t xml:space="preserve">LevelDesign_001</t>
   </si>
 </sst>
 </file>
@@ -72,7 +65,7 @@
   <numFmts count="1">
     <numFmt numFmtId="164" formatCode="General"/>
   </numFmts>
-  <fonts count="6">
+  <fonts count="5">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -101,13 +94,6 @@
       <color theme="1"/>
       <name val="Calibri"/>
       <family val="2"/>
-      <charset val="1"/>
-    </font>
-    <font>
-      <sz val="10"/>
-      <color theme="1"/>
-      <name val="Liberation Mono;Courier New;DejaVu Sans Mono"/>
-      <family val="3"/>
       <charset val="1"/>
     </font>
   </fonts>
@@ -172,7 +158,7 @@
     <xf numFmtId="42" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
     <xf numFmtId="9" fontId="1" fillId="0" borderId="0" applyFont="true" applyBorder="false" applyAlignment="false" applyProtection="false"/>
   </cellStyleXfs>
-  <cellXfs count="8">
+  <cellXfs count="7">
     <xf numFmtId="164" fontId="0" fillId="0" borderId="0" xfId="0" applyFont="false" applyBorder="false" applyAlignment="false" applyProtection="false">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
@@ -198,10 +184,6 @@
       <protection locked="true" hidden="false"/>
     </xf>
     <xf numFmtId="164" fontId="0" fillId="2" borderId="1" xfId="0" applyFont="false" applyBorder="true" applyAlignment="true" applyProtection="true">
-      <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
-      <protection locked="true" hidden="false"/>
-    </xf>
-    <xf numFmtId="164" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="true" applyBorder="false" applyAlignment="true" applyProtection="true">
       <alignment horizontal="general" vertical="bottom" textRotation="0" wrapText="false" indent="0" shrinkToFit="false"/>
       <protection locked="true" hidden="false"/>
     </xf>
@@ -764,39 +746,4 @@
     <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
   </headerFooter>
 </worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:xdr="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing" xmlns:x14="http://schemas.microsoft.com/office/spreadsheetml/2009/9/main" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
-  <sheetPr filterMode="false">
-    <pageSetUpPr fitToPage="false"/>
-  </sheetPr>
-  <dimension ref="A1:B2"/>
-  <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="12.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
-  <sheetData>
-    <row r="1" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A1" s="7" t="s">
-        <v>0</v>
-      </c>
-      <c r="B1" s="1" t="s">
-        <v>12</v>
-      </c>
-    </row>
-    <row r="2" customFormat="false" ht="13.8" hidden="false" customHeight="false" outlineLevel="0" collapsed="false">
-      <c r="A2" s="1" t="n">
-        <v>1</v>
-      </c>
-      <c r="B2" s="1" t="s">
-        <v>13</v>
-      </c>
-    </row>
-  </sheetData>
-  <printOptions headings="false" gridLines="false" gridLinesSet="true" horizontalCentered="false" verticalCentered="false"/>
-  <pageMargins left="0.7875" right="0.7875" top="1.05277777777778" bottom="1.05277777777778" header="0.7875" footer="0.7875"/>
-  <pageSetup paperSize="1" scale="100" fitToWidth="1" fitToHeight="1" pageOrder="downThenOver" orientation="portrait" blackAndWhite="false" draft="false" cellComments="none" horizontalDpi="300" verticalDpi="300" copies="1"/>
-  <headerFooter differentFirst="false" differentOddEven="false">
-    <oddHeader>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;Kffffff&amp;A</oddHeader>
-    <oddFooter>&amp;C&amp;"Times New Roman,Regular"&amp;12&amp;KffffffPage &amp;P</oddFooter>
-  </headerFooter>
-</worksheet>
 </file>
--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -52,10 +52,10 @@
     <t xml:space="preserve">Spawn_Random</t>
   </si>
   <si>
-    <t xml:space="preserve">10000_10, 10010_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10010_3,10000_1</t>
+    <t xml:space="preserve">10001_10, 10011_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">10011_3,10001_1</t>
   </si>
 </sst>
 </file>

--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -52,10 +52,10 @@
     <t xml:space="preserve">Spawn_Random</t>
   </si>
   <si>
-    <t xml:space="preserve">10001_10, 10011_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">10011_3,10001_1</t>
+    <t xml:space="preserve">1001_10, 1011_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1011_3,1001_1</t>
   </si>
 </sst>
 </file>
@@ -439,8 +439,14 @@
   <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="7.93"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.34"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6.85"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.43"/>
   </cols>
   <sheetData>

--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -439,13 +439,13 @@
   <dimension ref="A1:I1048576"/>
   <sheetFormatPr defaultColWidth="11.53515625" defaultRowHeight="13.8" customHeight="false" zeroHeight="false" outlineLevelRow="0" outlineLevelCol="0"/>
   <cols>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="0" width="7.55"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="0" width="7.83"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="0" width="7.97"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="1" min="1" style="1" width="7.55"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="2" min="2" style="1" width="7.83"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="3" min="3" style="1" width="7.97"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="4" min="4" style="1" width="6.85"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="0" width="10.61"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="0" width="8.95"/>
-    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="0" width="7.14"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="5" min="5" style="1" width="10.61"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="6" min="6" style="1" width="8.95"/>
+    <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="7" min="7" style="1" width="7.16"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="8" min="8" style="1" width="15.99"/>
     <col collapsed="false" customWidth="true" hidden="false" outlineLevel="0" max="9" min="9" style="1" width="17.43"/>
   </cols>
@@ -496,10 +496,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>10</v>
+        <v>1000</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>50</v>
+        <v>10000</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>9</v>

--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -52,10 +52,10 @@
     <t xml:space="preserve">Spawn_Random</t>
   </si>
   <si>
-    <t xml:space="preserve">1001_10, 1011_2</t>
-  </si>
-  <si>
-    <t xml:space="preserve">1011_3,1001_1</t>
+    <t xml:space="preserve">1001_10, 1002_2</t>
+  </si>
+  <si>
+    <t xml:space="preserve">1002_3,1001_1</t>
   </si>
 </sst>
 </file>

--- a/light_fight/Assets/Excels/LevelConfig.xlsx
+++ b/light_fight/Assets/Excels/LevelConfig.xlsx
@@ -496,10 +496,10 @@
         <v>0</v>
       </c>
       <c r="F2" s="1" t="n">
-        <v>1000</v>
+        <v>10</v>
       </c>
       <c r="G2" s="1" t="n">
-        <v>10000</v>
+        <v>54</v>
       </c>
       <c r="H2" s="1" t="s">
         <v>9</v>
